--- a/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEB6E3A-4164-4C65-840C-6B9177AC915F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A9FAF-6CAB-47E5-8893-BF9825780512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -75,10 +78,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Posture</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>属性集名:生成代码时会用到，需要符合C#的变量命名规范</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -136,6 +135,22 @@
   </si>
   <si>
     <t>##var</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpMax</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="26.5546875" customWidth="1"/>
@@ -509,7 +524,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -532,7 +547,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -543,29 +558,29 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -576,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -588,10 +603,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -652,7 +667,7 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -671,7 +686,7 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -697,7 +712,7 @@
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -723,16 +738,16 @@
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+        <v>29</v>
+      </c>
+      <c r="G10" s="2">
+        <v>100</v>
+      </c>
+      <c r="H10" s="2">
         <v>0</v>
       </c>
       <c r="I10" s="2">
@@ -749,33 +764,45 @@
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="1"/>
-      <c r="I11" s="2"/>
+      <c r="E11" s="1">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>999</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="2">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="1">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2">
         <v>100</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
         <v>999</v>
       </c>
       <c r="J12" t="b">
@@ -786,18 +813,19 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <v>4</v>
+      <c r="E13" s="1">
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13">
+        <v>32</v>
+      </c>
+      <c r="G13" s="2">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2">
         <v>0</v>
       </c>
       <c r="I13" s="2">
@@ -811,26 +839,76 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>999</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>999</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
@@ -855,21 +933,36 @@
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2"/>
+      <c r="B27" s="1"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A9FAF-6CAB-47E5-8893-BF9825780512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F79DE7-9476-42A3-96CA-6CB2B9E68B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -82,38 +76,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>*attribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>array,attributeInSet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>initValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>minValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>useMinValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>useMaxValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FightUnit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -151,6 +113,46 @@
   </si>
   <si>
     <t>SpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*Attribute</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>array,AttributeInSet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseMinValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseMaxValue</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -515,16 +517,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -535,19 +537,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -558,43 +560,43 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -603,16 +605,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" s="2">
         <v>100</v>
@@ -639,7 +641,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -664,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -690,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -716,7 +718,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -742,7 +744,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2">
         <v>100</v>
@@ -768,7 +770,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G11" s="2">
         <v>100</v>
@@ -794,7 +796,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2">
         <v>100</v>
@@ -820,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G13" s="2">
         <v>100</v>
@@ -851,16 +853,16 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2">
         <v>3</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -885,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>10</v>
